--- a/healthcare_forms/005_doctor_information_form--healthcare_forms.xlsx
+++ b/healthcare_forms/005_doctor_information_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_two</t>
+          <t>page_two_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_two</t>
+          <t>page_two_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_two</t>
+          <t>page_two_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact info</t>
+          <t>Page Two 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_one</t>
+          <t>page_one_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_one</t>
+          <t>page_one_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_one</t>
+          <t>page_one_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>page_three_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>page_three_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>page_three_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medical school</t>
+          <t>Page Three 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>page_three_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>page_three_6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>specialties</t>
+          <t>Page Three 6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>page_three_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -875,7 +875,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -900,7 +900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_two_choices</t>
+          <t>page_two_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_two_choices</t>
+          <t>page_two_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_two_choices</t>
+          <t>page_two_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_two_choices</t>
+          <t>page_two_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_three_choices</t>
+          <t>page_three_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_three_choices</t>
+          <t>page_three_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_three_choices</t>
+          <t>page_three_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_three_choices</t>
+          <t>page_three_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_three_choices</t>
+          <t>page_three_6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_three_choices</t>
+          <t>page_three_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
